--- a/www/download/COUNTRY.HUN.WIOD16.xlsx
+++ b/www/download/COUNTRY.HUN.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Hungria</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>281.056773468241</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>286.339323551982</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>256.916183664241</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>224.143380037342</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>202.390228599763</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>199.142095851074</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>210.114491386356</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>183.369823928295</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>170.35688062923</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>200.723810059073</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>207.195484795995</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>199.826151248414</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>224.910148395716</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>223.600595671987</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>232.165078657529</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.237</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.227</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>4.227</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4.186</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>4.174</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4.192</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>4.198</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>4.116</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4.013</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>4.002</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>4.003</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>4.008</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>4.046</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>4.234</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3.526</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3.586</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>3.599</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>3.645</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>3.617</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>3.643</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3.681</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>3.711</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>3.646</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3.564</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>3.567</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>3.575</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>3.578</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>3.647</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>3.834</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>8478.118</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>8303.851</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>8347.633</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>8224.11</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>8273.34</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>8293.71</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>8312.569</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>8286.024</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>8132.385</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>7861.527</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>7012.817</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>6995.249</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>6927.549</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>6974.654</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>7336.303</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7043.947</t>
+          <t>10851335469.5955</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7028.262</t>
+          <t>10723263156.0312</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7096.729</t>
+          <t>10807504367.8531</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7084.115</t>
+          <t>10629350037.7584</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7141.998</t>
+          <t>10462374680.1655</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7232.103</t>
+          <t>10380100210.7231</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7293.256</t>
+          <t>10499923839.0396</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>7320.774</t>
+          <t>10275374955.4287</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7200.055</t>
+          <t>10010051380.7472</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6978.606</t>
+          <t>9324236384.76808</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>6247.67</t>
+          <t>8704089609.20302</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>6244.206</t>
+          <t>8913235717.31457</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>6179.156</t>
+          <t>8217610551.81153</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>6282.516</t>
+          <t>8176658291.43953</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>6639.684</t>
+          <t>8898464415.45085</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1999963233.34973</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2045024048.45562</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2195185661.03394</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2287727257.69535</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2134135712.46185</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2031517900.68685</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1956853416.78495</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1884662634.43198</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1827808515.14141</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1729885465.67635</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1483258675.12768</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1479118578.72673</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1395718928.77889</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1416792768.55772</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1552741289.75753</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5769482.96057996</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5021775.19751621</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4253831.06007248</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3487459.65197834</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2782567.28812688</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2585629.87874834</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2493205.73525021</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2062302.02502355</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1739123.81498932</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2099124.41550614</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1881580.84591644</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1708086.85648455</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1786809.0133575</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1681009.33390959</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1730279.59907127</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>42884.2898554268</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>41123.0580144139</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>41486.9060192493</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>43709.6425483492</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>47663.1384850289</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>49778.1996089882</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>52696.244355256</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>57628.2892775637</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>59583.9532169001</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>52964.3039782264</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>52013.3089393725</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>55778.0308112324</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>51833.388518636</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>50252.2997584965</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>52836.5565003522</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>88171.074075256</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>86311.4776296078</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>87511.6462055534</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>93668.699031557</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>101931.407740804</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>108580.841477803</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>116032.725612693</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>128206.831252899</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>135562.526649701</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>114914.453083988</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>118844.261690612</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>129241.232189508</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>116098.408825391</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>115405.014722637</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>126174.346487731</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2.52203824677423</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2.43676251890909</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2.23286049374859</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2.09657323711591</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2.34655287304165</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2.55995041813555</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2.72703235584329</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2.88439493957836</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2.93917357335594</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3.03414338027953</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>3.21212436155964</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3.22157228622954</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>3.42722089139118</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>3.4343224636836</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>3.27610448939426</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>20883.9606121056</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>21515.4563726258</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>24321.2030480575</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>30155.7364611995</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>35152.5336673479</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>36752.6750679954</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>38426.596531965</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>48643.7023392876</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>55165.8502685804</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>49542.6913689474</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>50596.3521227293</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>55055.6539272067</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>51283.5925832792</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>52933.641177849</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>52130.7198318834</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>281.056773468241</t>
+          <t>567.193286959627</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>286.339323551982</t>
+          <t>570.338838211309</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>256.916183664241</t>
+          <t>609.983900297307</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>224.143380037342</t>
+          <t>627.675692691797</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>202.390228599763</t>
+          <t>590.008020851298</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>199.142095851074</t>
+          <t>557.651242711851</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>210.114491386356</t>
+          <t>531.56586444597</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>183.369823928295</t>
+          <t>507.858430189161</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>170.35688062923</t>
+          <t>501.32297170339</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>200.723810059073</t>
+          <t>485.333939061686</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>207.195484795995</t>
+          <t>415.82339282085</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>199.826151248414</t>
+          <t>413.71168892906</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>224.910148395716</t>
+          <t>390.133703265061</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>223.600595671987</t>
+          <t>388.512595889919</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>232.165078657529</t>
+          <t>404.979836248612</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-882040405.241259</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-623174100.23061</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>-295227267.896493</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>-134405680.513853</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>-41662322.2984083</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-26322167.4351351</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>66434264.2553672</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>157658569.293227</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>266131855.680123</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>116490060.757092</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>309822496.022833</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>472167838.159516</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>301122734.715384</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>577448891.707687</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>782981779.024426</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>-839936472.013438</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>-609441952.217453</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-214728756.665416</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>53557216.8590619</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>131724432.310966</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>208152504.998183</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>216559812.064955</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>308285832.949999</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>436776352.871988</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>311324830.680642</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>511645601.151663</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>670017529.308513</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>491149728.410164</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>744950250.490224</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>868322706.601149</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>-42103933.2278218</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>-13732148.013158</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>-80498511.231077</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>-187962897.372915</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>-173386754.609375</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>-234474672.433318</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>-150125547.809588</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>-150627263.656772</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>-170644497.191865</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>-194834769.92355</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>-201823105.12883</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.587</t>
+          <t>-197849691.148997</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>-190026993.69478</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>-167501358.782537</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>-85340927.5767238</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>1997.67644998539</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1960.11914224279</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>1971.99285309384</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>1943.64375157761</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>1974.49303729753</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>1985.21077466587</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1981.16317605194</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>1972.72271624899</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>1974.79820185026</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1957.90669749069</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>1751.49984300709</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>1746.51380047214</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>1727.20808153088</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1722.79013137869</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>1731.73609589684</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>2000.94347420594</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>1962.93231361579</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1974.85497301645</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1945.63692137598</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>1976.22326403678</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>1986.90296092765</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1982.85135023943</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1973.77448511719</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>1976.02856394359</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>1959.01980198316</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1752.51199741721</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1747.60652225315</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>1728.32696648683</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>1723.90320481778</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>1732.77354291401</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>27939.8529918095</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30714.9096769734</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>35669.1026923311</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>44066.6151370763</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>58085.4548028165</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>65741.408719463</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>80857.896706311</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>101166.038032998</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>116514.290350351</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>87165.7939380749</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>98970.2975738897</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>115363.280783742</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>103266.143884812</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>109576.952886719</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>116445.030855706</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3057833321.34786</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3145453427.31236</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>3196633787.92088</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>3224034758.56785</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>3498680664.48362</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3641632705.01575</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>4134092254.67841</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>4396849616.27862</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>4441246305.15359</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>3905433288.05301</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>3996191565.95839</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>4287355007.67131</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>3931734069.20112</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>3910146377.38691</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>4190295112.47144</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>30117.4279123389</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>31965.6250647104</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>36575.3439670472</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>46239.0957076052</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>59775.6234894592</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>66518.6111406065</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>80540.0987652225</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>97760.2512285331</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>113390.814464032</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>81578.1114610883</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>91471.0065171828</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>106233.196171305</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>94281.8062970353</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>98858.3405747733</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>105504.272342488</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8478.118</t>
+          <t>2512230306.51934</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8303.851</t>
+          <t>2722506214.78771</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8347.633</t>
+          <t>3047742341.67228</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8224.11</t>
+          <t>3420164576.14594</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8273.34</t>
+          <t>3690253146.94078</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>8293.71</t>
+          <t>3713309598.77913</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8312.569</t>
+          <t>4164053817.28577</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>8286.024</t>
+          <t>4221419848.23843</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>8132.385</t>
+          <t>4438473486.34673</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>7861.527</t>
+          <t>3477963351.13682</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>7012.817</t>
+          <t>3657454529.86181</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>6995.249</t>
+          <t>4010405579.65565</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>6927.549</t>
+          <t>3487794212.72632</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>6974.654</t>
+          <t>3593769079.44698</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>7336.303</t>
+          <t>4069832084.46913</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>7043.947</t>
+          <t>-2177.57492052943</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7028.262</t>
+          <t>-1250.71538773709</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>7096.729</t>
+          <t>-906.241274716163</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7084.115</t>
+          <t>-2172.48057052896</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>7141.998</t>
+          <t>-1690.1686866427</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>7232.103</t>
+          <t>-777.202421143476</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7293.256</t>
+          <t>317.797941088535</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>7320.774</t>
+          <t>3405.78680446454</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>7200.055</t>
+          <t>3123.47588631948</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>6978.606</t>
+          <t>5587.68247698664</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>6247.67</t>
+          <t>7499.29105670691</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>6244.206</t>
+          <t>9130.0846124375</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>6179.156</t>
+          <t>8984.33758777647</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>6282.516</t>
+          <t>10718.6123119453</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>6639.684</t>
+          <t>10940.7585132173</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>10852.418</t>
+          <t>545603014.828519</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10725.497</t>
+          <t>422947212.524651</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>10810.678</t>
+          <t>148891446.2486</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>10631.393</t>
+          <t>-196129817.578093</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>10463.944</t>
+          <t>-191572482.457162</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10381.258</t>
+          <t>-71676893.7633737</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>10501.07</t>
+          <t>-29961562.6073643</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>10279.994</t>
+          <t>175429768.040187</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>10010.646</t>
+          <t>2772818.80686291</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>9324.705</t>
+          <t>427469936.91619</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>8706.525</t>
+          <t>338737036.096579</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>8916.442</t>
+          <t>276949428.015664</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>8218.747</t>
+          <t>443939856.474793</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>8176.603</t>
+          <t>316377297.939934</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>8897.61</t>
+          <t>120463028.002304</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>20347.675416</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>23078.04222636</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>28600.52992848</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>35767.44046005</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>44182.43440835</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>47673.66216282</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>48218.51140848</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>57366.70175412</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>62892.9102272</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>50518.77999434</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>50413.59376284</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>55404.64514195</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>50187.09951736</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>52898.27589436</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>56206.36865568</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5277.829</t>
+          <t>-0.0171345146533971</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5109.093</t>
+          <t>-0.00700102903317167</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5123.546</t>
+          <t>0.00574543548482289</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4960.089</t>
+          <t>0.00218787734949265</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4892.208</t>
+          <t>0.00665745697073016</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>4758.691</t>
+          <t>0.0107220314362033</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4768.539</t>
+          <t>0.0119853542744352</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>4618.726</t>
+          <t>0.0056765353458746</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>4399.729</t>
+          <t>0.00574549809637431</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4297.559</t>
+          <t>-0.00266223313822512</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>3809.427</t>
+          <t>-0.00154729443553493</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>3846.781</t>
+          <t>-0.00112568957327501</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>3668.841</t>
+          <t>-0.00673755749993031</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>3560.468</t>
+          <t>-0.00202032197390669</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>3726.306</t>
+          <t>0.0033462825834773</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>20558.814252</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>23551.25002164</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>29317.30844112</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>37929.65912526</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>45786.59288105</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50417.86347126</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>50843.43744933</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>62020.34095014</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>70373.71167938</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>57608.41724057</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>55695.7600276</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>59686.3019454</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>54166.57312664</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>56538.68658984</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>57740.25998016</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2000.17</t>
+          <t>23323.49442822</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2045.356</t>
+          <t>26563.201154658</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2195.624</t>
+          <t>32899.2686231328</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2288.122</t>
+          <t>42159.1833246455</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2134.28</t>
+          <t>50944.4144677055</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2031.616</t>
+          <t>55710.836036881</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1957.198</t>
+          <t>55921.1215869662</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1885.088</t>
+          <t>67895.288784639</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1827.541</t>
+          <t>77030.9644760446</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1729.932</t>
+          <t>63007.0092146915</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1483.592</t>
+          <t>60690.4730205928</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1479.505</t>
+          <t>65146.131968567</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1395.811</t>
+          <t>59194.6354353728</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1416.784</t>
+          <t>61494.0029505594</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1552.489</t>
+          <t>62694.0329448552</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>252.17</t>
+          <t>221912.45957304</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>243.62</t>
+          <t>238870.439199676</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>223.22</t>
+          <t>280745.257041739</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>209.6</t>
+          <t>342718.129409854</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>234.63</t>
+          <t>402410.731562834</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>255.98</t>
+          <t>431350.285276898</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>272.64</t>
+          <t>445519.00923802</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>288.35</t>
+          <t>547909.126799881</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>293.97</t>
+          <t>631333.466278238</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>303.4</t>
+          <t>558249.666539423</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>321.12</t>
+          <t>552111.452277222</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>322.05</t>
+          <t>587205.424204613</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>342.69</t>
+          <t>534262.242358152</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>343.44</t>
+          <t>550723.040794777</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>327.68</t>
+          <t>545284.418647407</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>40363.063516791</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5.023</t>
+          <t>41203.8108021139</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4.255</t>
+          <t>42119.4760951501</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.488</t>
+          <t>44709.4337997231</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.783</t>
+          <t>46490.8446774462</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.586</t>
+          <t>48519.7668015506</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.494</t>
+          <t>49052.6513855672</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.063</t>
+          <t>49480.4838458157</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.739</t>
+          <t>49684.53796618</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.099</t>
+          <t>45984.9099117185</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.882</t>
+          <t>44741.10986484</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.709</t>
+          <t>45356.682199711</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>45590.0845187934</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.681</t>
+          <t>45973.5451985663</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>47072.2548501442</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>36233.1900811954</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>37023.6278624555</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>38092.4334099558</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>40555.2429662119</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>41848.1987989612</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>43873.3132966721</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>44660.1892513858</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>45492.087931896</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>45172.1538510526</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>41689.2035091661</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>41058.99978</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>41674.1266507778</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>42065.1936366883</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>42595.9187211204</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>43573.4023043593</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>17081.59832178</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>19843.1174926224</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>25934.2068100608</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>30905.5616937958</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>37831.5657972875</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>41377.6263867496</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>43766.299693678</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>51753.9278638944</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>58793.1754972594</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>48056.500607283</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>49742.0731448256</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>54394.642903809</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>47683.9700053494</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>51821.0033169946</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>53955.3955850448</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>7043947000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7028262000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>7096729000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>7084115000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>7141998000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>7232103000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>7293256000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>7320774000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>7200055000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>6978606000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>6247670000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>6244206000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>6179156000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>6282516000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>6639684000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>8478117556.81902</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8303851454.25828</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>8347632976.7416</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>8224109984.81019</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>8273340121.49415</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>8293710470.47457</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>8312568916.01426</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>8286023714.99105</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>8132385075.48112</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>7861526875.1604</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>7012816958.62474</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>6995249483.01401</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>6927549280.15119</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>6974653781.212</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>7336303264.66647</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5277828590.35402</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5109093077.5356</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5123545693.09081</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>4960089074.31474</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>4892207655.27961</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>4758691249.93203</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>4768538784.31244</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4618726432.74995</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>4399729393.58401</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4297559419.15114</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>3809426685.30391</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>3846781155.252</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>3668840983.57889</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>3560468186.51475</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>3726305948.40497</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4237060</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4230330</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4226960</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4226950</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4186440</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4174190</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4192230</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4198060</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4115520</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4012990</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>4001580</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>4002760</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>4008240</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>4045850</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>4233850</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3526070</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3585630</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3598760</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3644760</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3617130</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3642990</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3681300</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3711000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3645970</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3564320</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>3567040</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>3575240</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>3577540</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>3646710</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>3834120</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>8478117556.81902</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8303851454.25828</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>8347632976.7416</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>8224109984.81019</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>8273340121.49415</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>8293710470.47457</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>8312568916.01426</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>8286023714.99105</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>8132385075.48112</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7861526875.1604</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>7012816958.62474</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>6995249483.01401</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>6927549280.15119</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>6974653781.212</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>7336303264.66647</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>7043947000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7028262000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>7096729000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>7084115000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>7141998000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>7232103000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>7293256000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>7320774000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>7200055000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6978606000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>6247670000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>6244206000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>6179156000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>6282516000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>6639684000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>98593.855818</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>110350.79851428</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>134515.43031312</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>167628.85878557</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>203622.5873409</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>227451.12632476</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>239637.48367748</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>286482.18051702</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>329371.23990971</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>260315.30083363</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>265080.12012944</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>292185.89576605</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>258209.98925234</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>270431.95398596</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>284429.54634624</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>40405.09275</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>46406.31903144</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>58833.47551104</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>73064.74541997</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>88775.98056145</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>97088.462976</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>99687.42213732</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>119649.21779376</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>135824.14114731</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>111063.51056927</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>110432.546455</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>119540.77507255</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>106878.60539626</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>113315.00671478</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>116649.42960672</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>367095.121867078</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>365821.111308726</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>363898.008995804</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>370785.361376856</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>377924.229594726</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>379913.827511798</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>389792.949217942</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>395274.145959904</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>402494.499987158</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>412473.336048234</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>407017.410056928</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>407942.040483573</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>407588.953915795</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>414822.328039702</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>422134.933237948</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
